--- a/artfynd/A 3304-2025 artfynd.xlsx
+++ b/artfynd/A 3304-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AY6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121158825</v>
+        <v>97505929</v>
       </c>
       <c r="B2" t="n">
-        <v>100370</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>56835</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,41 +686,56 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>222498</v>
+        <v>205995</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Dvärgpipistrell</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Pipistrellus pygmaeus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr"/>
-      <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
-      <c r="N2" t="inlineStr"/>
+          <t>(W.E.Leach, 1825)</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>registreringar</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>autobox med tidsexpansion</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Sävja, Upl</t>
+          <t>Uppsala, Upl</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>650753</v>
+        <v>650693</v>
       </c>
       <c r="R2" t="n">
-        <v>6633137</v>
+        <v>6633147</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -749,12 +759,22 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2024-04-10</t>
+          <t>2021-07-20</t>
+        </is>
+      </c>
+      <c r="Z2" t="inlineStr">
+        <is>
+          <t>21:30</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2024-04-10</t>
+          <t>2021-07-21</t>
+        </is>
+      </c>
+      <c r="AB2" t="inlineStr">
+        <is>
+          <t>04:30</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -763,80 +783,85 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
-      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Kirsi Jokinen</t>
+          <t>Martin Brüsin</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Anna Broberg</t>
-        </is>
-      </c>
-      <c r="AY2" t="inlineStr">
-        <is>
-          <t>Naturvärdesinventering vid Sweco</t>
-        </is>
-      </c>
+          <t>Johanna Kammonen, Emily Macgregor</t>
+        </is>
+      </c>
+      <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121158821</v>
+        <v>97505930</v>
       </c>
       <c r="B3" t="n">
-        <v>100370</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>56816</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>222498</v>
+        <v>205998</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Nordfladdermus</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Eptesicus nilssonii</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
-      <c r="N3" t="inlineStr"/>
+          <t>(A.Keyserling &amp; Blasius, 1839)</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>registreringar</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>autobox med tidsexpansion</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Sävja, Upl</t>
+          <t>Uppsala, Upl</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>650842</v>
+        <v>650693</v>
       </c>
       <c r="R3" t="n">
-        <v>6633410</v>
+        <v>6633147</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -860,12 +885,22 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2024-04-19</t>
+          <t>2021-07-20</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>21:30</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2024-04-19</t>
+          <t>2021-07-21</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>04:30</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -874,22 +909,335 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
-      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
+          <t>Martin Brüsin</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>Johanna Kammonen, Emily Macgregor</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>121158821</v>
+      </c>
+      <c r="B4" t="n">
+        <v>101326</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Sävja, Upl</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>650842</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6633410</v>
+      </c>
+      <c r="S4" t="n">
+        <v>10</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Danmark</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2024-04-19</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2024-04-19</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF4" t="inlineStr"/>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
           <t>Kirsi Jokinen</t>
         </is>
       </c>
-      <c r="AX3" t="inlineStr">
+      <c r="AX4" t="inlineStr">
         <is>
           <t>Viktor Bolin</t>
         </is>
       </c>
-      <c r="AY3" t="inlineStr">
+      <c r="AY4" t="inlineStr">
+        <is>
+          <t>Naturvärdesinventering vid Sweco</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>121158825</v>
+      </c>
+      <c r="B5" t="n">
+        <v>101326</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Sävja, Upl</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>650753</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6633137</v>
+      </c>
+      <c r="S5" t="n">
+        <v>10</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Danmark</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2024-04-10</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2024-04-10</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF5" t="inlineStr"/>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Kirsi Jokinen</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Anna Broberg</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr">
+        <is>
+          <t>Naturvärdesinventering vid Sweco</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>121158826</v>
+      </c>
+      <c r="B6" t="n">
+        <v>101326</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Sävja, Upl</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>650779</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6633164</v>
+      </c>
+      <c r="S6" t="n">
+        <v>10</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Danmark</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2024-04-10</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2024-04-10</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF6" t="inlineStr"/>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Kirsi Jokinen</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Anna Broberg</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr">
         <is>
           <t>Naturvärdesinventering vid Sweco</t>
         </is>
